--- a/00_output/00_Master_Input_Template.xlsx
+++ b/00_output/00_Master_Input_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5350DC026F49FED1593B64338BB45A54E3093A46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_6C2E2964CD9AC690F1A3F81E633A59FAE9AADC43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2C556DE-881A-4553-9698-960AA9893AA2}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kwh_kw_ratio" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="122">
   <si>
     <t>parent_condition_name</t>
   </si>
@@ -68,69 +68,9 @@
     <t>multifamily_li</t>
   </si>
   <si>
-    <t>large_restaurant</t>
-  </si>
-  <si>
-    <t>large_hospital</t>
-  </si>
-  <si>
-    <t>large_hotel</t>
-  </si>
-  <si>
-    <t>large_office</t>
-  </si>
-  <si>
-    <t>large_outpatient</t>
-  </si>
-  <si>
-    <t>large_primary_secondary_school</t>
-  </si>
-  <si>
-    <t>large_retail</t>
-  </si>
-  <si>
-    <t>large_strip_mall</t>
-  </si>
-  <si>
-    <t>large_warehouse</t>
-  </si>
-  <si>
-    <t>small_restaurant</t>
-  </si>
-  <si>
-    <t>small_hospital</t>
-  </si>
-  <si>
-    <t>small_hotel</t>
-  </si>
-  <si>
-    <t>small_office</t>
-  </si>
-  <si>
-    <t>small_outpatient</t>
-  </si>
-  <si>
-    <t>small_primary_secondary_school</t>
-  </si>
-  <si>
-    <t>small_retail</t>
-  </si>
-  <si>
-    <t>small_strip_mall</t>
-  </si>
-  <si>
-    <t>small_warehouse</t>
-  </si>
-  <si>
     <t>furnace</t>
   </si>
   <si>
-    <t>central_ac</t>
-  </si>
-  <si>
-    <t>room_ac</t>
-  </si>
-  <si>
     <t>fridge</t>
   </si>
   <si>
@@ -149,7 +89,322 @@
     <t>none</t>
   </si>
   <si>
-    <t>competition_group_subgroup</t>
+    <t>competition_group</t>
+  </si>
+  <si>
+    <t>subgroup</t>
+  </si>
+  <si>
+    <t>heating_cooling</t>
+  </si>
+  <si>
+    <t>oil_furnace</t>
+  </si>
+  <si>
+    <t>gas_furnace</t>
+  </si>
+  <si>
+    <t>refrigeration</t>
+  </si>
+  <si>
+    <t>full_size</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>furnace_efficient_oil_residential</t>
+  </si>
+  <si>
+    <t>furnace_baseline_oil_residential</t>
+  </si>
+  <si>
+    <t>furnace_existing_oil_residential</t>
+  </si>
+  <si>
+    <t>furnace_efficient_natural_gas_residential</t>
+  </si>
+  <si>
+    <t>furnace_baseline_natural_gas_residential</t>
+  </si>
+  <si>
+    <t>furnace_existing_natural_gas_residential</t>
+  </si>
+  <si>
+    <t>fridge_efficient_electric_residential</t>
+  </si>
+  <si>
+    <t>fridge_baseline_electric_residential</t>
+  </si>
+  <si>
+    <t>fridge_top10_electric_residential</t>
+  </si>
+  <si>
+    <t>fridge_existing_electric_residential</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>summer_on-peak_usdperKWH</t>
+  </si>
+  <si>
+    <t>summer_off-peak_usdperKWH</t>
+  </si>
+  <si>
+    <t>winter_on-peak_usdperKWH</t>
+  </si>
+  <si>
+    <t>winter_off-peak_usdperKWH</t>
+  </si>
+  <si>
+    <t>shoulder_on-peak_usdperKWH</t>
+  </si>
+  <si>
+    <t>shoulder_off-peak_usdperKWH</t>
+  </si>
+  <si>
+    <t>summer_gener_capacity_usdperKWH</t>
+  </si>
+  <si>
+    <t>winter_gener_capacity_usdperKWH</t>
+  </si>
+  <si>
+    <t>summer_td_usdperKWH</t>
+  </si>
+  <si>
+    <t>winter_td_usdperKWH</t>
+  </si>
+  <si>
+    <t>oil_residential_usdperMMBtu</t>
+  </si>
+  <si>
+    <t>natural_gas_residential_usdperMMBtu</t>
+  </si>
+  <si>
+    <t>summer_on-peak_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>summer_off-peak_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>winter_on-peak_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>winter_off-peak_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>shoulder_on-peak_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>shoulder_off-peak_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>summer_gener_capacity_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>winter_gener_capacity_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>summer_td_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>winter_td_usdperKWH_carbon</t>
+  </si>
+  <si>
+    <t>oil_residential_usdperMMBtu_carbon</t>
+  </si>
+  <si>
+    <t>natural_gas_residential_usdperMMBtu_carbon</t>
+  </si>
+  <si>
+    <t>summer_on-peak_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>summer_off-peak_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>winter_on-peak_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>winter_off-peak_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>shoulder_on-peak_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>shoulder_off-peak_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>summer_gener_capacity_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>winter_gener_capacity_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>summer_td_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>winter_td_usdperKWH_n2o</t>
+  </si>
+  <si>
+    <t>oil_residential_usdperMMBtu_n2o</t>
+  </si>
+  <si>
+    <t>natural_gas_residential_usdperMMBtu_n2o</t>
+  </si>
+  <si>
+    <t>summer_on-peak_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>summer_off-peak_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>winter_on-peak_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>winter_off-peak_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>shoulder_on-peak_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>shoulder_off-peak_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>summer_gener_capacity_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>winter_gener_capacity_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>summer_td_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>winter_td_usdperKWH_ch4</t>
+  </si>
+  <si>
+    <t>oil_residential_usdperMMBtu_ch4</t>
+  </si>
+  <si>
+    <t>natural_gas_residential_usdperMMBtu_ch4</t>
+  </si>
+  <si>
+    <t>unique_measure_name</t>
+  </si>
+  <si>
+    <t>summer_on-peak</t>
+  </si>
+  <si>
+    <t>summer_off-peak</t>
+  </si>
+  <si>
+    <t>winter_on-peak</t>
+  </si>
+  <si>
+    <t>winter_off-peak</t>
+  </si>
+  <si>
+    <t>shoulder_on-peak</t>
+  </si>
+  <si>
+    <t>shoulder_off-peak</t>
+  </si>
+  <si>
+    <t>summer_gener_capacity</t>
+  </si>
+  <si>
+    <t>winter_gener_capacity</t>
+  </si>
+  <si>
+    <t>summer_td</t>
+  </si>
+  <si>
+    <t>winter_td</t>
+  </si>
+  <si>
+    <t>utility</t>
+  </si>
+  <si>
+    <t>electric_incentive_percentage</t>
+  </si>
+  <si>
+    <t>gas_incentive_percentage</t>
+  </si>
+  <si>
+    <t>nonutility_incentive_percentage</t>
+  </si>
+  <si>
+    <t>program</t>
+  </si>
+  <si>
+    <t>fuel</t>
+  </si>
+  <si>
+    <t>non-incentive_costs_as_a_percent_of_incentive_costs</t>
+  </si>
+  <si>
+    <t>nlirnc</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>natural_gas</t>
+  </si>
+  <si>
+    <t>electric</t>
+  </si>
+  <si>
+    <t>nlirrepl</t>
+  </si>
+  <si>
+    <t>nlirret</t>
+  </si>
+  <si>
+    <t>lirnc</t>
+  </si>
+  <si>
+    <t>lirrepl</t>
+  </si>
+  <si>
+    <t>lirret</t>
+  </si>
+  <si>
+    <t>scinc</t>
+  </si>
+  <si>
+    <t>scirepl</t>
+  </si>
+  <si>
+    <t>sciret</t>
+  </si>
+  <si>
+    <t>lcinc</t>
+  </si>
+  <si>
+    <t>lcirepl</t>
+  </si>
+  <si>
+    <t>lciret</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>other_nonresource_benefit</t>
+  </si>
+  <si>
+    <t>electric_residential_usdperKWH</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>competition_subgroup</t>
   </si>
   <si>
     <t>heating_cooling_oil_furnace</t>
@@ -158,373 +413,7 @@
     <t>heating_cooling_gas_furnace</t>
   </si>
   <si>
-    <t>heating_cooling_cooling</t>
-  </si>
-  <si>
     <t>refrigeration_full_size</t>
-  </si>
-  <si>
-    <t>measure_name_competition_subgroup</t>
-  </si>
-  <si>
-    <t>furnace_efficient_oil_residential_heating_cooling_oil_furnace</t>
-  </si>
-  <si>
-    <t>furnace_baseline_oil_residential_heating_cooling_oil_furnace</t>
-  </si>
-  <si>
-    <t>furnace_existing_oil_residential_heating_cooling_oil_furnace</t>
-  </si>
-  <si>
-    <t>furnace_efficient_natural_gas_residential_heating_cooling_gas_furnace</t>
-  </si>
-  <si>
-    <t>furnace_baseline_natural_gas_residential_heating_cooling_gas_furnace</t>
-  </si>
-  <si>
-    <t>furnace_existing_natural_gas_residential_heating_cooling_gas_furnace</t>
-  </si>
-  <si>
-    <t>central_ac_efficient_electric_residential_heating_cooling_cooling</t>
-  </si>
-  <si>
-    <t>central_ac_baseline_electric_residential_heating_cooling_cooling</t>
-  </si>
-  <si>
-    <t>central_ac_existing_electric_residential_heating_cooling_cooling</t>
-  </si>
-  <si>
-    <t>room_ac_efficient_electric_residential_heating_cooling_cooling</t>
-  </si>
-  <si>
-    <t>room_ac_baseline_electric_residential_heating_cooling_cooling</t>
-  </si>
-  <si>
-    <t>room_ac_existing_electric_residential_heating_cooling_cooling</t>
-  </si>
-  <si>
-    <t>fridge_efficient_electric_residential_refrigeration_full_size</t>
-  </si>
-  <si>
-    <t>fridge_baseline_electric_residential_refrigeration_full_size</t>
-  </si>
-  <si>
-    <t>fridge_top10_electric_residential_refrigeration_full_size</t>
-  </si>
-  <si>
-    <t>fridge_existing_electric_residential_refrigeration_full_size</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>summer_on-peak_usdperKWH</t>
-  </si>
-  <si>
-    <t>summer_off-peak_usdperKWH</t>
-  </si>
-  <si>
-    <t>winter_on-peak_usdperKWH</t>
-  </si>
-  <si>
-    <t>winter_off-peak_usdperKWH</t>
-  </si>
-  <si>
-    <t>shoulder_on-peak_usdperKWH</t>
-  </si>
-  <si>
-    <t>shoulder_off-peak_usdperKWH</t>
-  </si>
-  <si>
-    <t>summer_gener._capacity_usdperKWH</t>
-  </si>
-  <si>
-    <t>winter_gener_capacity_usdperKWH</t>
-  </si>
-  <si>
-    <t>summer_td_usdperKWH</t>
-  </si>
-  <si>
-    <t>winter_td_usdperKWH</t>
-  </si>
-  <si>
-    <t>oil_residential_usdperMMBtu</t>
-  </si>
-  <si>
-    <t>natural_gas_residential_usdperMMBtu</t>
-  </si>
-  <si>
-    <t>summer_on-peak_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>summer_off-peak_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>winter_on-peak_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>winter_off-peak_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>shoulder_on-peak_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>shoulder_off-peak_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>summer_gener._capacity_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>winter_gener_capacity_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>summer_td_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>winter_td_usdperKWH_carbon</t>
-  </si>
-  <si>
-    <t>oil_residential_usdperMMBtu_carbon</t>
-  </si>
-  <si>
-    <t>natural_gas_residential_usdperMMBtu_carbon</t>
-  </si>
-  <si>
-    <t>summer_on-peak_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>summer_off-peak_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>winter_on-peak_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>winter_off-peak_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>shoulder_on-peak_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>shoulder_off-peak_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>summer_gener._capacity_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>winter_gener_capacity_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>summer_td_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>winter_td_usdperKWH_n2o</t>
-  </si>
-  <si>
-    <t>oil_residential_usdperMMBtu_n2o</t>
-  </si>
-  <si>
-    <t>natural_gas_residential_usdperMMBtu_n2o</t>
-  </si>
-  <si>
-    <t>summer_on-peak_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>summer_off-peak_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>winter_on-peak_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>winter_off-peak_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>shoulder_on-peak_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>shoulder_off-peak_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>summer_gener._capacity_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>winter_gener_capacity_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>summer_td_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>winter_td_usdperKWH_ch4</t>
-  </si>
-  <si>
-    <t>oil_residential_usdperMMBtu_ch4</t>
-  </si>
-  <si>
-    <t>natural_gas_residential_usdperMMBtu_ch4</t>
-  </si>
-  <si>
-    <t>unique_measure_name</t>
-  </si>
-  <si>
-    <t>summer_on-peak</t>
-  </si>
-  <si>
-    <t>summer_off-peak</t>
-  </si>
-  <si>
-    <t>winter_on-peak</t>
-  </si>
-  <si>
-    <t>winter_off-peak</t>
-  </si>
-  <si>
-    <t>shoulder_on-peak</t>
-  </si>
-  <si>
-    <t>shoulder_off-peak</t>
-  </si>
-  <si>
-    <t>summer_gener._capacity</t>
-  </si>
-  <si>
-    <t>winter_gener_capacity</t>
-  </si>
-  <si>
-    <t>summer_td</t>
-  </si>
-  <si>
-    <t>winter_td</t>
-  </si>
-  <si>
-    <t>furnace_efficient_oil_residential</t>
-  </si>
-  <si>
-    <t>furnace_baseline_oil_residential</t>
-  </si>
-  <si>
-    <t>furnace_existing_oil_residential</t>
-  </si>
-  <si>
-    <t>furnace_efficient_natural_gas_residential</t>
-  </si>
-  <si>
-    <t>furnace_baseline_natural_gas_residential</t>
-  </si>
-  <si>
-    <t>furnace_existing_natural_gas_residential</t>
-  </si>
-  <si>
-    <t>central_ac_efficient_electric_residential</t>
-  </si>
-  <si>
-    <t>central_ac_baseline_electric_residential</t>
-  </si>
-  <si>
-    <t>central_ac_existing_electric_residential</t>
-  </si>
-  <si>
-    <t>room_ac_efficient_electric_residential</t>
-  </si>
-  <si>
-    <t>room_ac_baseline_electric_residential</t>
-  </si>
-  <si>
-    <t>room_ac_existing_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_efficient_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_baseline_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_top10_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_existing_electric_residential</t>
-  </si>
-  <si>
-    <t>utility</t>
-  </si>
-  <si>
-    <t>electric_incentive_percentage</t>
-  </si>
-  <si>
-    <t>gas_incentive_percentage</t>
-  </si>
-  <si>
-    <t>nonutility_incentive_percentage</t>
-  </si>
-  <si>
-    <t>program</t>
-  </si>
-  <si>
-    <t>fuel</t>
-  </si>
-  <si>
-    <t>non-incentive_costs_as_a_percent_of_incentive_costs</t>
-  </si>
-  <si>
-    <t>nlirnc</t>
-  </si>
-  <si>
-    <t>oil</t>
-  </si>
-  <si>
-    <t>natural_gas</t>
-  </si>
-  <si>
-    <t>electric</t>
-  </si>
-  <si>
-    <t>nlirrepl</t>
-  </si>
-  <si>
-    <t>nlirret</t>
-  </si>
-  <si>
-    <t>lirnc</t>
-  </si>
-  <si>
-    <t>lirrepl</t>
-  </si>
-  <si>
-    <t>lirret</t>
-  </si>
-  <si>
-    <t>scinc</t>
-  </si>
-  <si>
-    <t>scirepl</t>
-  </si>
-  <si>
-    <t>sciret</t>
-  </si>
-  <si>
-    <t>lcinc</t>
-  </si>
-  <si>
-    <t>lcirepl</t>
-  </si>
-  <si>
-    <t>lciret</t>
-  </si>
-  <si>
-    <t>sector</t>
-  </si>
-  <si>
-    <t>residential</t>
-  </si>
-  <si>
-    <t>other_nonresource_benefit</t>
-  </si>
-  <si>
-    <t>electric_residential_usdperKWH</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>competition_subgroup</t>
   </si>
 </sst>
 </file>
@@ -864,10 +753,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -886,79 +778,15 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -973,42 +801,42 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="J1" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="K1" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1023,25 +851,25 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1051,24 +879,24 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1076,7 +904,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1084,7 +912,7 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1092,7 +920,7 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1100,7 +928,7 @@
         <v>2027</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,7 +936,7 @@
         <v>2027</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1116,7 +944,7 @@
         <v>2027</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1124,7 +952,7 @@
         <v>2028</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1132,7 +960,7 @@
         <v>2028</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1140,7 +968,7 @@
         <v>2028</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1148,7 +976,7 @@
         <v>2029</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1156,7 +984,7 @@
         <v>2029</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1164,7 +992,7 @@
         <v>2029</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1172,7 +1000,7 @@
         <v>2030</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1180,7 +1008,7 @@
         <v>2030</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1188,7 +1016,7 @@
         <v>2030</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1196,7 +1024,7 @@
         <v>2031</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1204,7 +1032,7 @@
         <v>2031</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1212,7 +1040,7 @@
         <v>2031</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1220,7 +1048,7 @@
         <v>2032</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1228,7 +1056,7 @@
         <v>2032</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1236,7 +1064,7 @@
         <v>2032</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1244,7 +1072,7 @@
         <v>2033</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1252,7 +1080,7 @@
         <v>2033</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1260,7 +1088,7 @@
         <v>2033</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1268,7 +1096,7 @@
         <v>2034</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1276,7 +1104,7 @@
         <v>2034</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1284,7 +1112,7 @@
         <v>2034</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1292,7 +1120,7 @@
         <v>2035</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1300,7 +1128,7 @@
         <v>2035</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1308,7 +1136,247 @@
         <v>2035</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2036</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2036</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2036</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2037</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2037</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2037</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2038</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2038</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2038</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2039</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2039</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2039</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2040</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2040</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2040</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2041</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2041</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2041</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2042</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2042</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2042</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2043</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2043</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2043</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2044</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2044</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2044</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2045</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2045</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2045</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1318,95 +1386,65 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1416,12 +1454,12 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1435,79 +1473,20 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1517,12 +1496,12 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1536,79 +1515,20 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1618,12 +1538,12 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1637,79 +1557,20 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1719,15 +1580,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1741,115 +1602,29 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1859,98 +1634,51 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="B4" t="s">
         <v>19</v>
-      </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1960,158 +1688,140 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2121,48 +1831,48 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="M1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -2213,6 +1923,56 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2035</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2045</v>
       </c>
     </row>
   </sheetData>
@@ -2222,120 +1982,120 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" t="s">
+      <c r="N1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" t="s">
+        <v>64</v>
+      </c>
+      <c r="W1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
+      <c r="AA1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" t="s">
+      <c r="AB1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" t="s">
+      <c r="AC1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" t="s">
+      <c r="AD1" t="s">
         <v>72</v>
       </c>
-      <c r="G1" t="s">
+      <c r="AE1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" t="s">
+      <c r="AF1" t="s">
         <v>74</v>
       </c>
-      <c r="I1" t="s">
+      <c r="AG1" t="s">
         <v>75</v>
       </c>
-      <c r="J1" t="s">
+      <c r="AH1" t="s">
         <v>76</v>
       </c>
-      <c r="K1" t="s">
+      <c r="AI1" t="s">
         <v>77</v>
       </c>
-      <c r="L1" t="s">
+      <c r="AJ1" t="s">
         <v>78</v>
       </c>
-      <c r="M1" t="s">
+      <c r="AK1" t="s">
         <v>79</v>
-      </c>
-      <c r="N1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O1" t="s">
-        <v>81</v>
-      </c>
-      <c r="P1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R1" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T1" t="s">
-        <v>86</v>
-      </c>
-      <c r="U1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
@@ -2386,6 +2146,56 @@
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2035</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2045</v>
       </c>
     </row>
   </sheetData>
@@ -2395,122 +2205,105 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="J1" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="K1" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2520,408 +2313,271 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>119</v>
-      </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>130</v>
-      </c>
-      <c r="B49" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2936,1204 +2592,1204 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B78" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B86" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B91" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B98" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/00_output/00_Master_Input_Template.xlsx
+++ b/00_output/00_Master_Input_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_6D2E096FEB8A058FF1E375BB2FABED34082AEED9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD565DE-18E5-4D31-BB64-B514B8DD990E}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_6D2E444D64121799F1F3FEF50FE8F908A12CD9E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3DFB46E-77E7-4EC1-8B11-A30694C9FC09}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kwh_kw_ratio" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
     <t>furnace</t>
   </si>
   <si>
-    <t>fridge</t>
+    <t>refrigerator</t>
   </si>
   <si>
     <t>electric_utility</t>
@@ -118,16 +118,16 @@
     <t>furnace_natural_gas_existing_residential</t>
   </si>
   <si>
-    <t>fridge_electric_efficient_residential</t>
-  </si>
-  <si>
-    <t>fridge_electric_baseline_residential</t>
-  </si>
-  <si>
-    <t>fridge_electric_top10_residential</t>
-  </si>
-  <si>
-    <t>fridge_electric_existing_residential</t>
+    <t>refrigerator_electric_efficient_residential</t>
+  </si>
+  <si>
+    <t>refrigerator_electric_baseline_residential</t>
+  </si>
+  <si>
+    <t>refrigerator_electric_top10_residential</t>
+  </si>
+  <si>
+    <t>refrigerator_electric_existing_residential</t>
   </si>
   <si>
     <t>year</t>
@@ -1566,6 +1566,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1621,8 +1629,11 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1679,9 +1690,7 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1826,6 +1835,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2200,6 +2212,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2295,6 +2317,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/00_output/00_Master_Input_Template.xlsx
+++ b/00_output/00_Master_Input_Template.xlsx
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1272,68 +1272,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
@@ -1603,7 +1645,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1734,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,7 +1829,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1846,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1863,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1875,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1892,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
@@ -1867,78 +1909,180 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
@@ -2437,7 +2581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,68 +2644,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
@@ -2578,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2611,7 +2797,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2623,7 +2809,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2635,7 +2821,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2647,7 +2833,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2659,7 +2845,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2671,7 +2857,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2683,7 +2869,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2695,7 +2881,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2707,7 +2893,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2719,7 +2905,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>refrigerator_electric_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2731,79 +2917,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_natural_gas_baseline_residential_2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_natural_gas_existing_residential_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2815,7 +3001,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2827,7 +3013,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2839,7 +3025,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>refrigerator_electric_existing_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2851,118 +3037,334 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_baseline_residential_2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_existing_residential_2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_existing_residential</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/00_output/00_Master_Input_Template.xlsx
+++ b/00_output/00_Master_Input_Template.xlsx
@@ -477,7 +477,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -564,8 +564,8 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,7 +657,7 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -712,12 +712,12 @@
   <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5447,11 +5447,11 @@
   <dimension ref="A1:G577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
   </cols>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7681,12 +7681,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8116,12 +8116,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -9044,12 +9044,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -10378,12 +10378,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -10465,12 +10465,12 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -10552,12 +10552,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -10610,12 +10610,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -10668,12 +10668,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -11770,12 +11770,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12321,12 +12321,12 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -12350,12 +12350,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12379,12 +12379,12 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -13162,12 +13162,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -13220,12 +13220,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -13278,12 +13278,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -13423,12 +13423,12 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -13539,12 +13539,12 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -13626,12 +13626,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -13655,12 +13655,12 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -13684,12 +13684,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -13713,12 +13713,12 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -13771,12 +13771,12 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -13829,12 +13829,12 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -14728,12 +14728,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -14757,12 +14757,12 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -14786,12 +14786,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -14815,12 +14815,12 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -14873,12 +14873,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -14902,12 +14902,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -14960,12 +14960,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -15018,12 +15018,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -15047,12 +15047,12 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -15134,12 +15134,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -15163,12 +15163,12 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -15192,12 +15192,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -15221,12 +15221,12 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -15946,12 +15946,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -15975,12 +15975,12 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
@@ -16062,12 +16062,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -16091,12 +16091,12 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -16149,12 +16149,12 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
@@ -16178,12 +16178,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -16207,12 +16207,12 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
@@ -16236,12 +16236,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -16265,12 +16265,12 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -16323,12 +16323,12 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -16410,12 +16410,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -16439,12 +16439,12 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
@@ -16468,12 +16468,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -16497,12 +16497,12 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
@@ -16526,12 +16526,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -16555,12 +16555,12 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -16613,12 +16613,12 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -17338,12 +17338,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -17367,12 +17367,12 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
@@ -17396,12 +17396,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -17425,12 +17425,12 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
@@ -17454,12 +17454,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -17483,12 +17483,12 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr">
@@ -17512,12 +17512,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -17541,12 +17541,12 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr">
@@ -17570,12 +17570,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr">
@@ -17628,12 +17628,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
@@ -17686,12 +17686,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -17715,12 +17715,12 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E423" s="4" t="inlineStr">
@@ -17744,12 +17744,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -17773,12 +17773,12 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E425" s="4" t="inlineStr">
@@ -17802,12 +17802,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -17831,12 +17831,12 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -17889,12 +17889,12 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
@@ -17918,12 +17918,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -17947,12 +17947,12 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E431" s="4" t="inlineStr">
@@ -17976,12 +17976,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -18005,12 +18005,12 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E433" s="4" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -18730,12 +18730,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -18759,12 +18759,12 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E459" s="4" t="inlineStr">
@@ -18788,12 +18788,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -18817,12 +18817,12 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E461" s="4" t="inlineStr">
@@ -18846,12 +18846,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -18875,12 +18875,12 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E463" s="4" t="inlineStr">
@@ -18904,12 +18904,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -18933,12 +18933,12 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E465" s="4" t="inlineStr">
@@ -18962,12 +18962,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -18991,12 +18991,12 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E467" s="4" t="inlineStr">
@@ -19020,12 +19020,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -19049,12 +19049,12 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E469" s="4" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -19107,12 +19107,12 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E471" s="4" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -19165,12 +19165,12 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E473" s="4" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E475" s="4" t="inlineStr">
@@ -19252,12 +19252,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E477" s="4" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -19339,12 +19339,12 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E479" s="4" t="inlineStr">
@@ -19368,12 +19368,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -19397,12 +19397,12 @@
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E481" s="4" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
@@ -19600,7 +19600,7 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -19745,7 +19745,7 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -20151,12 +20151,12 @@
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E507" s="4" t="inlineStr">
@@ -20180,12 +20180,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -20209,12 +20209,12 @@
       </c>
       <c r="C509" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E509" s="4" t="inlineStr">
@@ -20238,12 +20238,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -20267,12 +20267,12 @@
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E511" s="4" t="inlineStr">
@@ -20296,12 +20296,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -20325,12 +20325,12 @@
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E513" s="4" t="inlineStr">
@@ -20354,12 +20354,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -20383,12 +20383,12 @@
       </c>
       <c r="C515" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E515" s="4" t="inlineStr">
@@ -20412,12 +20412,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -20441,12 +20441,12 @@
       </c>
       <c r="C517" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E517" s="4" t="inlineStr">
@@ -20470,12 +20470,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -20499,12 +20499,12 @@
       </c>
       <c r="C519" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E519" s="4" t="inlineStr">
@@ -20528,12 +20528,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -20557,12 +20557,12 @@
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E521" s="4" t="inlineStr">
@@ -20586,12 +20586,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
@@ -20615,12 +20615,12 @@
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E523" s="4" t="inlineStr">
@@ -20644,12 +20644,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -20673,12 +20673,12 @@
       </c>
       <c r="C525" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E525" s="4" t="inlineStr">
@@ -20702,12 +20702,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -20731,12 +20731,12 @@
       </c>
       <c r="C527" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E527" s="4" t="inlineStr">
@@ -20760,12 +20760,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -20789,12 +20789,12 @@
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E529" s="4" t="inlineStr">
@@ -20818,7 +20818,7 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D531" s="4" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D533" s="4" t="inlineStr">
@@ -20934,7 +20934,7 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D535" s="4" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
@@ -21021,7 +21021,7 @@
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
@@ -21079,7 +21079,7 @@
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D541" s="4" t="inlineStr">
@@ -21514,12 +21514,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
@@ -21543,12 +21543,12 @@
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E555" s="4" t="inlineStr">
@@ -21572,12 +21572,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
@@ -21601,12 +21601,12 @@
       </c>
       <c r="C557" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E557" s="4" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -21659,12 +21659,12 @@
       </c>
       <c r="C559" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E559" s="4" t="inlineStr">
@@ -21688,12 +21688,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -21717,12 +21717,12 @@
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E561" s="4" t="inlineStr">
@@ -21746,12 +21746,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
@@ -21775,12 +21775,12 @@
       </c>
       <c r="C563" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E563" s="4" t="inlineStr">
@@ -21804,12 +21804,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -21833,12 +21833,12 @@
       </c>
       <c r="C565" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E565" s="4" t="inlineStr">
@@ -21862,12 +21862,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
@@ -21891,12 +21891,12 @@
       </c>
       <c r="C567" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E567" s="4" t="inlineStr">
@@ -21920,12 +21920,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr">
@@ -21949,12 +21949,12 @@
       </c>
       <c r="C569" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E569" s="4" t="inlineStr">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -22007,12 +22007,12 @@
       </c>
       <c r="C571" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E571" s="4" t="inlineStr">
@@ -22036,12 +22036,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -22065,12 +22065,12 @@
       </c>
       <c r="C573" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E573" s="4" t="inlineStr">
@@ -22094,12 +22094,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -22123,12 +22123,12 @@
       </c>
       <c r="C575" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
@@ -22152,12 +22152,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -22181,12 +22181,12 @@
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
@@ -22212,8 +22212,8 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22371,7 +22371,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -22600,7 +22600,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -22829,7 +22829,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -23058,7 +23058,7 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
@@ -23288,7 +23288,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -23537,7 +23537,7 @@
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -23932,7 +23932,7 @@
   <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
@@ -24369,7 +24369,7 @@
   <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
@@ -25430,7 +25430,7 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -25439,8 +25439,8 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25787,8 +25787,8 @@
   <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -25859,7 +25859,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -25877,7 +25877,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -25895,7 +25895,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -26039,12 +26039,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -26057,12 +26057,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
@@ -26075,12 +26075,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -26093,12 +26093,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
@@ -26111,12 +26111,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -26129,12 +26129,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
@@ -26147,12 +26147,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
@@ -26165,12 +26165,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
@@ -26183,12 +26183,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D22" s="3" t="n"/>
@@ -26201,12 +26201,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
@@ -26219,12 +26219,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
@@ -26237,12 +26237,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
@@ -26262,8 +26262,8 @@
   <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="53" customWidth="1" min="4" max="4"/>
   </cols>
@@ -26298,7 +26298,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -26316,7 +26316,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -26442,7 +26442,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -26712,7 +26712,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -26730,7 +26730,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -26838,7 +26838,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -27054,7 +27054,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -27072,7 +27072,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -27090,7 +27090,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -27198,7 +27198,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -27306,7 +27306,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -27522,7 +27522,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -27612,7 +27612,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -27720,7 +27720,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -27774,7 +27774,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -27810,7 +27810,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -28026,7 +28026,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -28170,7 +28170,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -28188,7 +28188,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -28278,7 +28278,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -28404,7 +28404,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -28440,7 +28440,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -28458,7 +28458,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -28566,7 +28566,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -28584,7 +28584,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -28602,7 +28602,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -28620,7 +28620,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -28656,7 +28656,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -28692,7 +28692,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -28710,7 +28710,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -28818,7 +28818,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
